--- a/templates/office/Phase1_요구사항추적표_RTM.xlsx
+++ b/templates/office/Phase1_요구사항추적표_RTM.xlsx
@@ -1352,7 +1352,7 @@
       </c>
       <c r="C12" s="59" t="inlineStr">
         <is>
-          <t>아모레퍼시픽 SyncGuard AI 시스템 구축</t>
+          <t>한빛글로벌 SyncGuard AI 시스템 구축</t>
         </is>
       </c>
       <c r="D12" s="60" t="n"/>
@@ -1410,13 +1410,13 @@
     <row r="22" ht="18.75" customHeight="1">
       <c r="C22" s="68" t="inlineStr">
         <is>
-          <t>그로브 (EMPASY)</t>
+          <t>엠파시 (EMPASY)</t>
         </is>
       </c>
       <c r="D22" s="69" t="n"/>
       <c r="E22" s="65" t="inlineStr">
         <is>
-          <t>아모레퍼시픽</t>
+          <t>한빛글로벌</t>
         </is>
       </c>
       <c r="F22" s="66" t="n"/>
@@ -1438,13 +1438,13 @@
     <row r="24" ht="84" customHeight="1" thickBot="1">
       <c r="C24" s="57" t="inlineStr">
         <is>
-          <t>그로브소프트 (EMPASY)</t>
+          <t>엠파시 (EMPASY)</t>
         </is>
       </c>
       <c r="D24" s="58" t="n"/>
       <c r="E24" s="61" t="inlineStr">
         <is>
-          <t>아모레퍼시픽</t>
+          <t>한빛글로벌</t>
         </is>
       </c>
       <c r="F24" s="62" t="n"/>
@@ -1543,17 +1543,17 @@
       </c>
       <c r="D4" s="55" t="inlineStr">
         <is>
-          <t>요구사항정의서(EMP_ANL_020) 최신 내역(동영상 장면 캡처, 티움넷/마이비커 연계, KT레몬 Option) 동기화</t>
+          <t>요구사항정의서(EMP_ANL_020) 최신 내역(동영상 장면 캡처, 마케팅허브/프로덕트랩 연계, KT레몬 Option) 동기화</t>
         </is>
       </c>
       <c r="E4" s="54" t="inlineStr">
         <is>
-          <t>그로브소프트</t>
+          <t>엠파시</t>
         </is>
       </c>
       <c r="F4" s="56" t="inlineStr">
         <is>
-          <t>아모레퍼시픽 RA</t>
+          <t>한빛글로벌 RA</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
     <row r="2" ht="18" customHeight="1" thickBot="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>프로젝트 명 : 아모레퍼시픽 SyncGuard AI 시스템 구축</t>
+          <t>프로젝트 명 : 한빛글로벌 SyncGuard AI 시스템 구축</t>
         </is>
       </c>
       <c r="B2" s="7" t="n"/>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="C39" s="47" t="inlineStr">
         <is>
-          <t>티움넷(MarketingHub) 양방향 API 연동</t>
+          <t>마케팅허브(MarketingHub) 양방향 API 연동</t>
         </is>
       </c>
       <c r="D39" s="46" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="E39" s="47" t="inlineStr">
         <is>
-          <t>티움넷(MarketingHub) 양방향 API 연동</t>
+          <t>마케팅허브(MarketingHub) 양방향 API 연동</t>
         </is>
       </c>
       <c r="F39" s="46" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="C40" s="47" t="inlineStr">
         <is>
-          <t>마이비커(ProductLab) 실증·전성분 연계 및 [Option] KT 레몬 연동</t>
+          <t>프로덕트랩(ProductLab) 실증·전성분 연계 및 [Option] KT 레몬 연동</t>
         </is>
       </c>
       <c r="D40" s="46" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="E40" s="47" t="inlineStr">
         <is>
-          <t>마이비커(ProductLab) 실증·전성분 연계 및 [Option] KT 레몬 연동</t>
+          <t>프로덕트랩(ProductLab) 실증·전성분 연계 및 [Option] KT 레몬 연동</t>
         </is>
       </c>
       <c r="F40" s="46" t="inlineStr">

--- a/templates/office/Phase1_요구사항추적표_RTM.xlsx
+++ b/templates/office/Phase1_요구사항추적표_RTM.xlsx
@@ -1352,7 +1352,7 @@
       </c>
       <c r="C12" s="59" t="inlineStr">
         <is>
-          <t>한빛글로벌 SyncGuard AI 시스템 구축</t>
+          <t>한빛글로벌 SyncFlow AI 시스템 구축</t>
         </is>
       </c>
       <c r="D12" s="60" t="n"/>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="D4" s="55" t="inlineStr">
         <is>
-          <t>요구사항정의서(EMP_ANL_020) 최신 내역(동영상 장면 캡처, 마케팅허브/프로덕트랩 연계, KT레몬 Option) 동기화</t>
+          <t>요구사항정의서(EMP_ANL_020) 최신 내역(설계도면 스냅샷 추출, 전자구매포털/피엘엠넥서스 연계, HB-Monitor Option) 동기화</t>
         </is>
       </c>
       <c r="E4" s="54" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="F4" s="56" t="inlineStr">
         <is>
-          <t>한빛글로벌 RA</t>
+          <t>한빛글로벌 QA</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
     <row r="2" ht="18" customHeight="1" thickBot="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>프로젝트 명 : 한빛글로벌 SyncGuard AI 시스템 구축</t>
+          <t>프로젝트 명 : 한빛글로벌 SyncFlow AI 시스템 구축</t>
         </is>
       </c>
       <c r="B2" s="7" t="n"/>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="C4" s="42" t="inlineStr">
         <is>
-          <t>문서 및 동영상 장면 파싱</t>
+          <t>문서 및 설계도면 장면 파싱</t>
         </is>
       </c>
       <c r="D4" s="41" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="E4" s="43" t="inlineStr">
         <is>
-          <t>문서 및 동영상 장면 파싱</t>
+          <t>문서 및 설계도면 장면 파싱</t>
         </is>
       </c>
       <c r="F4" s="44" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="G4" s="45" t="inlineStr">
         <is>
-          <t>review_request / review_document / review_video_snapshot</t>
+          <t>verify_request / verify_document / verify_video_snapshot</t>
         </is>
       </c>
       <c r="H4" s="44" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="G5" s="46" t="inlineStr">
         <is>
-          <t>review_video_snapshot / review_sentence</t>
+          <t>verify_video_snapshot / verify_sentence</t>
         </is>
       </c>
       <c r="H5" s="46" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="G6" s="46" t="inlineStr">
         <is>
-          <t>review_request / review_sentence</t>
+          <t>verify_request / verify_sentence</t>
         </is>
       </c>
       <c r="H6" s="46" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="G7" s="46" t="inlineStr">
         <is>
-          <t>review_request / review_sentence</t>
+          <t>verify_request / verify_sentence</t>
         </is>
       </c>
       <c r="H7" s="46" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="G8" s="46" t="inlineStr">
         <is>
-          <t>review_request / review_sentence</t>
+          <t>verify_request / verify_sentence</t>
         </is>
       </c>
       <c r="H8" s="46" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="G9" s="46" t="inlineStr">
         <is>
-          <t>review_request / review_sentence</t>
+          <t>verify_request / verify_sentence</t>
         </is>
       </c>
       <c r="H9" s="46" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="G10" s="46" t="inlineStr">
         <is>
-          <t>review_request / review_sentence</t>
+          <t>verify_request / verify_sentence</t>
         </is>
       </c>
       <c r="H10" s="46" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="G11" s="46" t="inlineStr">
         <is>
-          <t>review_request / review_sentence</t>
+          <t>verify_request / verify_sentence</t>
         </is>
       </c>
       <c r="H11" s="46" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="G12" s="46" t="inlineStr">
         <is>
-          <t>review_request / review_sentence</t>
+          <t>verify_request / verify_sentence</t>
         </is>
       </c>
       <c r="H12" s="46" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="G13" s="46" t="inlineStr">
         <is>
-          <t>review_request / review_sentence</t>
+          <t>verify_request / verify_sentence</t>
         </is>
       </c>
       <c r="H13" s="46" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="G14" s="46" t="inlineStr">
         <is>
-          <t>review_request / review_sentence</t>
+          <t>verify_request / verify_sentence</t>
         </is>
       </c>
       <c r="H14" s="46" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="G15" s="46" t="inlineStr">
         <is>
-          <t>review_request / review_sentence</t>
+          <t>verify_request / verify_sentence</t>
         </is>
       </c>
       <c r="H15" s="46" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="C16" s="47" t="inlineStr">
         <is>
-          <t>실증자료 필요 여부 판단</t>
+          <t>시험성적서 필요 여부 판단</t>
         </is>
       </c>
       <c r="D16" s="46" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="E16" s="47" t="inlineStr">
         <is>
-          <t>실증자료 필요 여부 판단</t>
+          <t>시험성적서 필요 여부 판단</t>
         </is>
       </c>
       <c r="F16" s="46" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="G16" s="46" t="inlineStr">
         <is>
-          <t>review_request / review_sentence</t>
+          <t>verify_request / verify_sentence</t>
         </is>
       </c>
       <c r="H16" s="46" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="G17" s="46" t="inlineStr">
         <is>
-          <t>review_request / review_sentence</t>
+          <t>verify_request / verify_sentence</t>
         </is>
       </c>
       <c r="H17" s="46" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="G18" s="46" t="inlineStr">
         <is>
-          <t>review_request / review_sentence</t>
+          <t>verify_request / verify_sentence</t>
         </is>
       </c>
       <c r="H18" s="46" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="C19" s="47" t="inlineStr">
         <is>
-          <t>SyncGuard AI 1차 검토 자동 파이프라인</t>
+          <t>SyncFlow AI 1차 검토 자동 파이프라인</t>
         </is>
       </c>
       <c r="D19" s="46" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="E19" s="47" t="inlineStr">
         <is>
-          <t>SyncGuard AI 1차 검토 자동 파이프라인</t>
+          <t>SyncFlow AI 1차 검토 자동 파이프라인</t>
         </is>
       </c>
       <c r="F19" s="46" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="G19" s="46" t="inlineStr">
         <is>
-          <t>review_request / review_sentence</t>
+          <t>verify_request / verify_sentence</t>
         </is>
       </c>
       <c r="H19" s="46" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="G20" s="46" t="inlineStr">
         <is>
-          <t>review_request / review_sentence</t>
+          <t>verify_request / verify_sentence</t>
         </is>
       </c>
       <c r="H20" s="46" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="G21" s="46" t="inlineStr">
         <is>
-          <t>review_request / review_sentence</t>
+          <t>verify_request / verify_sentence</t>
         </is>
       </c>
       <c r="H21" s="46" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="G22" s="46" t="inlineStr">
         <is>
-          <t>review_document / review_video_snapshot</t>
+          <t>verify_document / verify_video_snapshot</t>
         </is>
       </c>
       <c r="H22" s="46" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="G23" s="46" t="inlineStr">
         <is>
-          <t>review_request / review_sentence</t>
+          <t>verify_request / verify_sentence</t>
         </is>
       </c>
       <c r="H23" s="46" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="G24" s="46" t="inlineStr">
         <is>
-          <t>review_request / review_sentence</t>
+          <t>verify_request / verify_sentence</t>
         </is>
       </c>
       <c r="H24" s="46" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="C25" s="47" t="inlineStr">
         <is>
-          <t>실증자료 요청 안내 (메일 발송)</t>
+          <t>시험성적서 요청 안내 (메일 발송)</t>
         </is>
       </c>
       <c r="D25" s="46" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="E25" s="47" t="inlineStr">
         <is>
-          <t>실증자료 요청 안내 (메일 발송)</t>
+          <t>시험성적서 요청 안내 (메일 발송)</t>
         </is>
       </c>
       <c r="F25" s="46" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="G25" s="46" t="inlineStr">
         <is>
-          <t>review_request / review_sentence</t>
+          <t>verify_request / verify_sentence</t>
         </is>
       </c>
       <c r="H25" s="46" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="G26" s="46" t="inlineStr">
         <is>
-          <t>review_request / review_sentence</t>
+          <t>verify_request / verify_sentence</t>
         </is>
       </c>
       <c r="H26" s="46" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="G27" s="46" t="inlineStr">
         <is>
-          <t>review_request / review_sentence</t>
+          <t>verify_request / verify_sentence</t>
         </is>
       </c>
       <c r="H27" s="46" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="G28" s="46" t="inlineStr">
         <is>
-          <t>review_request / review_sentence</t>
+          <t>verify_request / verify_sentence</t>
         </is>
       </c>
       <c r="H28" s="46" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="C29" s="47" t="inlineStr">
         <is>
-          <t>검토 대상 문장 및 동영상 캡처 장면 편집기</t>
+          <t>검토 대상 문장 및 설계도면 도면 스냅샷 편집기</t>
         </is>
       </c>
       <c r="D29" s="46" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="E29" s="47" t="inlineStr">
         <is>
-          <t>검토 대상 문장 및 동영상 캡처 장면 편집기</t>
+          <t>검토 대상 문장 및 설계도면 도면 스냅샷 편집기</t>
         </is>
       </c>
       <c r="F29" s="46" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="G29" s="46" t="inlineStr">
         <is>
-          <t>review_video_snapshot / review_sentence</t>
+          <t>verify_video_snapshot / verify_sentence</t>
         </is>
       </c>
       <c r="H29" s="46" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="C30" s="47" t="inlineStr">
         <is>
-          <t>실증 검증 화면</t>
+          <t>시험검증 검증 화면</t>
         </is>
       </c>
       <c r="D30" s="46" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="E30" s="47" t="inlineStr">
         <is>
-          <t>실증 검증 화면</t>
+          <t>시험검증 검증 화면</t>
         </is>
       </c>
       <c r="F30" s="46" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="G30" s="46" t="inlineStr">
         <is>
-          <t>review_request / review_sentence</t>
+          <t>verify_request / verify_sentence</t>
         </is>
       </c>
       <c r="H30" s="46" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="G31" s="46" t="inlineStr">
         <is>
-          <t>review_request / review_sentence</t>
+          <t>verify_request / verify_sentence</t>
         </is>
       </c>
       <c r="H31" s="46" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="C32" s="47" t="inlineStr">
         <is>
-          <t>RA 최종 판정 입력 (피드백 UI)</t>
+          <t>QA 최종 판정 입력 (피드백 UI)</t>
         </is>
       </c>
       <c r="D32" s="46" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="E32" s="47" t="inlineStr">
         <is>
-          <t>RA 최종 판정 입력 (피드백 UI)</t>
+          <t>QA 최종 판정 입력 (피드백 UI)</t>
         </is>
       </c>
       <c r="F32" s="46" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="G32" s="46" t="inlineStr">
         <is>
-          <t>review_request / review_sentence</t>
+          <t>verify_request / verify_sentence</t>
         </is>
       </c>
       <c r="H32" s="46" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="G33" s="46" t="inlineStr">
         <is>
-          <t>review_request / review_sentence</t>
+          <t>verify_request / verify_sentence</t>
         </is>
       </c>
       <c r="H33" s="46" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="G34" s="46" t="inlineStr">
         <is>
-          <t>review_request / review_sentence</t>
+          <t>verify_request / verify_sentence</t>
         </is>
       </c>
       <c r="H34" s="46" t="inlineStr">
@@ -3580,7 +3580,7 @@
       </c>
       <c r="G35" s="46" t="inlineStr">
         <is>
-          <t>review_request / review_sentence</t>
+          <t>verify_request / verify_sentence</t>
         </is>
       </c>
       <c r="H35" s="46" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="G36" s="46" t="inlineStr">
         <is>
-          <t>review_request / review_sentence</t>
+          <t>verify_request / verify_sentence</t>
         </is>
       </c>
       <c r="H36" s="46" t="inlineStr">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="G37" s="46" t="inlineStr">
         <is>
-          <t>review_request / review_sentence</t>
+          <t>verify_request / verify_sentence</t>
         </is>
       </c>
       <c r="H37" s="46" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="G38" s="46" t="inlineStr">
         <is>
-          <t>review_request / review_sentence</t>
+          <t>verify_request / verify_sentence</t>
         </is>
       </c>
       <c r="H38" s="46" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="C39" s="47" t="inlineStr">
         <is>
-          <t>마케팅허브(MarketingHub) 양방향 API 연동</t>
+          <t>전자구매포털(SRM-Portal) 양방향 API 연동</t>
         </is>
       </c>
       <c r="D39" s="46" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="E39" s="47" t="inlineStr">
         <is>
-          <t>마케팅허브(MarketingHub) 양방향 API 연동</t>
+          <t>전자구매포털(SRM-Portal) 양방향 API 연동</t>
         </is>
       </c>
       <c r="F39" s="46" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="G39" s="46" t="inlineStr">
         <is>
-          <t>review_request / api_interface_log</t>
+          <t>verify_request / api_interface_log</t>
         </is>
       </c>
       <c r="H39" s="46" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="C40" s="47" t="inlineStr">
         <is>
-          <t>프로덕트랩(ProductLab) 실증·전성분 연계 및 [Option] KT 레몬 연동</t>
+          <t>피엘엠넥서스(PLM-Nexus) 시험검증·자재BOM 연계 및 [Option] HB-Monitor 연동</t>
         </is>
       </c>
       <c r="D40" s="46" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="E40" s="47" t="inlineStr">
         <is>
-          <t>프로덕트랩(ProductLab) 실증·전성분 연계 및 [Option] KT 레몬 연동</t>
+          <t>피엘엠넥서스(PLM-Nexus) 시험검증·자재BOM 연계 및 [Option] HB-Monitor 연동</t>
         </is>
       </c>
       <c r="F40" s="46" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="G40" s="46" t="inlineStr">
         <is>
-          <t>review_evidence / review_ingredient_spec</t>
+          <t>verify_evidence / verify_ingredient_spec</t>
         </is>
       </c>
       <c r="H40" s="46" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="G41" s="46" t="inlineStr">
         <is>
-          <t>review_request / review_sentence</t>
+          <t>verify_request / verify_sentence</t>
         </is>
       </c>
       <c r="H41" s="46" t="inlineStr">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="G42" s="46" t="inlineStr">
         <is>
-          <t>review_request / review_sentence</t>
+          <t>verify_request / verify_sentence</t>
         </is>
       </c>
       <c r="H42" s="46" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="G43" s="46" t="inlineStr">
         <is>
-          <t>review_request / review_sentence</t>
+          <t>verify_request / verify_sentence</t>
         </is>
       </c>
       <c r="H43" s="46" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="G44" s="50" t="inlineStr">
         <is>
-          <t>review_request / review_sentence</t>
+          <t>verify_request / verify_sentence</t>
         </is>
       </c>
       <c r="H44" s="50" t="inlineStr">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="G45" s="50" t="inlineStr">
         <is>
-          <t>review_request / review_sentence</t>
+          <t>verify_request / verify_sentence</t>
         </is>
       </c>
       <c r="H45" s="50" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="G46" s="50" t="inlineStr">
         <is>
-          <t>review_request / review_sentence</t>
+          <t>verify_request / verify_sentence</t>
         </is>
       </c>
       <c r="H46" s="50" t="inlineStr">
